--- a/InputData/indst/IFSR/Industrial Fuel Shifting Ratio.xlsx
+++ b/InputData/indst/IFSR/Industrial Fuel Shifting Ratio.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28025"/>
-  <workbookPr defaultThemeVersion="124226"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28429"/>
+  <workbookPr codeName="현재_통합_문서" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Modeling\EPS\US\eps-us\InputData\indst\IFSR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\kjh_local\NEXTgroup_local\2025_local\2. EPS\업데이트 파일\eps-southkorea-3.3.1_2025update_v4.0.3\InputData\indst\IFSR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A789A36B-610F-4F64-BA37-96262CAFB538}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{140327C6-5F5D-4260-81E6-586F7DE85766}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10" yWindow="10" windowWidth="19180" windowHeight="11260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9270" yWindow="1350" windowWidth="13530" windowHeight="10720" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="Calcs" sheetId="4" r:id="rId2"/>
     <sheet name="HPEbP" sheetId="5" r:id="rId3"/>
     <sheet name="IFSR-chemicals" sheetId="3" r:id="rId4"/>
-    <sheet name="ISFR-ironsteel" sheetId="6" r:id="rId5"/>
+    <sheet name="IFSR-ironsteel" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -176,7 +176,7 @@
         <vertAlign val="subscript"/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="맑은 고딕"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -186,7 +186,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="맑은 고딕"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -197,7 +197,7 @@
         <vertAlign val="subscript"/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="맑은 고딕"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -207,7 +207,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="맑은 고딕"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -218,7 +218,7 @@
         <vertAlign val="subscript"/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="맑은 고딕"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -228,7 +228,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="맑은 고딕"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -239,7 +239,7 @@
         <vertAlign val="subscript"/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="맑은 고딕"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -249,7 +249,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="맑은 고딕"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -260,7 +260,7 @@
         <vertAlign val="subscript"/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="맑은 고딕"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -270,7 +270,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="맑은 고딕"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -281,7 +281,7 @@
         <vertAlign val="subscript"/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="맑은 고딕"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -291,7 +291,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="맑은 고딕"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -302,7 +302,7 @@
         <vertAlign val="subscript"/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="맑은 고딕"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -312,7 +312,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="맑은 고딕"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -323,7 +323,7 @@
         <vertAlign val="subscript"/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="맑은 고딕"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -333,7 +333,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="맑은 고딕"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -349,7 +349,7 @@
         <vertAlign val="subscript"/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="맑은 고딕"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -359,7 +359,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="맑은 고딕"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -370,7 +370,7 @@
         <vertAlign val="subscript"/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="맑은 고딕"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -380,7 +380,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="맑은 고딕"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -391,7 +391,7 @@
         <vertAlign val="subscript"/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="맑은 고딕"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -401,7 +401,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="맑은 고딕"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -412,7 +412,7 @@
         <vertAlign val="subscript"/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="맑은 고딕"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -422,7 +422,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="맑은 고딕"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -433,7 +433,7 @@
         <vertAlign val="subscript"/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="맑은 고딕"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -443,7 +443,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="맑은 고딕"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -454,7 +454,7 @@
         <vertAlign val="subscript"/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="맑은 고딕"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -548,14 +548,14 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.000"/>
-    <numFmt numFmtId="169" formatCode="0.0000"/>
+    <numFmt numFmtId="176" formatCode="0.000"/>
+    <numFmt numFmtId="177" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -563,14 +563,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -578,7 +578,7 @@
       <i/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -586,8 +586,15 @@
       <vertAlign val="subscript"/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -628,7 +635,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -637,12 +644,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="백분율" xfId="1" builtinId="5"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -944,15 +951,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:B47"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -960,193 +968,194 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B4" s="2">
         <v>2024</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A13" s="1"/>
       <c r="B13" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B14" s="2">
         <v>2023</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="23" spans="1:1" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="24" spans="1:1" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>70</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -1154,13 +1163,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C6A4AC5-8865-4921-8E10-BDED8AECA8F6}">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="A2:C17"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="42.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="42.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -1168,7 +1178,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -1179,7 +1189,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -1190,7 +1200,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
@@ -1201,12 +1211,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" s="5" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -1217,7 +1227,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -1228,7 +1238,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -1239,12 +1249,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A12" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -1255,12 +1265,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A14" s="5" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -1269,24 +1279,26 @@
         <v>0.5371573604060913</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B17" s="6"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{221F3C08-152C-483E-8BAD-E349F8D44D7B}">
+  <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:AI8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="30.1796875" customWidth="1"/>
-    <col min="2" max="2" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.1640625" customWidth="1"/>
+    <col min="2" max="2" width="9.4140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>46</v>
       </c>
@@ -1393,7 +1405,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>47</v>
       </c>
@@ -1500,7 +1512,7 @@
         <v>0.77521306818181679</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>48</v>
       </c>
@@ -1607,7 +1619,7 @@
         <v>0.71951219512195119</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>49</v>
       </c>
@@ -1714,7 +1726,7 @@
         <v>0.57004830917874394</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>50</v>
       </c>
@@ -1821,7 +1833,7 @@
         <v>0.46274509803921571</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>51</v>
       </c>
@@ -1928,7 +1940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>52</v>
       </c>
@@ -2035,7 +2047,7 @@
         <v>0.77521306818181679</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>53</v>
       </c>
@@ -2143,28 +2155,29 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <sheetPr>
+  <sheetPr codeName="Sheet4">
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.26953125" customWidth="1"/>
+    <col min="2" max="2" width="21.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -2172,7 +2185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -2181,7 +2194,7 @@
         <v>0.57004830917874394</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -2190,7 +2203,7 @@
         <v>0.71951219512195119</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -2198,7 +2211,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -2206,7 +2219,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -2214,7 +2227,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -2222,7 +2235,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -2230,7 +2243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -2238,7 +2251,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -2247,28 +2260,29 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B027129-067E-4476-9765-AADE93F0284F}">
-  <sheetPr>
+  <sheetPr codeName="Sheet5">
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7265625" customWidth="1"/>
+    <col min="2" max="2" width="12.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -2276,7 +2290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -2285,7 +2299,7 @@
         <v>0.5371573604060913</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -2294,7 +2308,7 @@
         <v>0.71951219512195119</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -2302,7 +2316,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -2310,7 +2324,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -2318,7 +2332,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -2326,7 +2340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -2334,7 +2348,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -2342,7 +2356,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -2351,6 +2365,178 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
+    <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="40f4d404-d193-41dc-bb72-733c1e774208" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{924EE642-B4F4-4B23-B0F2-31B8ECE3AE08}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2761ECD9-4BAF-4FEF-84CF-ACEA8DA403AD}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CFDB67FF-060F-436C-97F0-43C02D645E35}"/>
 </file>